--- a/서버정보/20260901_리소스배포_개발.xlsx
+++ b/서버정보/20260901_리소스배포_개발.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2D9EDA-C443-46BE-BDE3-B2E8AD0FCB38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A83A38A-4A38-4107-80DC-744735E66371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="135" windowWidth="28800" windowHeight="15345" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -15366,7 +15366,7 @@
         <v>430</v>
       </c>
       <c r="D76" s="34" t="s">
-        <v>424</v>
+        <v>49</v>
       </c>
       <c r="E76" s="34" t="s">
         <v>426</v>
@@ -15417,6 +15417,12 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="문서" ma:contentTypeID="0x010100589F7F6AEE51BC4C92024CB999111E60" ma:contentTypeVersion="4" ma:contentTypeDescription="새 문서를 만듭니다." ma:contentTypeScope="" ma:versionID="7236b106e1291626cb10ba6ee71a9b94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="89f0f392-688b-4454-b192-0691f37dc811" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="39d8cc4ddeff20ae29b23e47bf838372" ns2:_="">
     <xsd:import namespace="89f0f392-688b-4454-b192-0691f37dc811"/>
@@ -15560,12 +15566,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAFDA824-0F2E-4C40-8FCD-BF3D34EF26B3}">
   <ds:schemaRefs>
@@ -15575,6 +15575,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B942A36D-0DEC-4379-B834-CD4D85F3BBDA}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15590,20 +15606,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF093BAC-4385-48E8-8492-BA8C8E7EF612}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="89f0f392-688b-4454-b192-0691f37dc811"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>